--- a/Luban/Excel/旅行对话.xlsx
+++ b/Luban/Excel/旅行对话.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <author>think</author>
   </authors>
   <commentList>
-    <comment ref="L2" authorId="0">
+    <comment ref="M2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
+    <comment ref="N2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,18 +87,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>关联主要角色</t>
-  </si>
-  <si>
-    <t>关联活动标签</t>
-  </si>
-  <si>
-    <t>内容</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>旅行事件id</t>
+  </si>
+  <si>
+    <t>对话角色id</t>
+  </si>
+  <si>
+    <t>应用表情</t>
+  </si>
+  <si>
+    <t>文本本地化</t>
   </si>
   <si>
     <t>上一节点ID</t>
@@ -122,16 +122,13 @@
     <t>参数变化</t>
   </si>
   <si>
-    <t>Id</t>
+    <t>#对话角色</t>
   </si>
   <si>
     <t>#内容</t>
   </si>
   <si>
     <t>#节点类型</t>
-  </si>
-  <si>
-    <t>int32</t>
   </si>
 </sst>
 </file>
@@ -160,14 +157,14 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -793,29 +790,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1129,88 +1117,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="11.7777777777778" style="1" customWidth="1"/>
     <col min="2" max="3" width="14.1111111111111" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="11.8888888888889" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="10" width="11.1111111111111" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.2" spans="1:13">
+    <row r="1" ht="16.2" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="16.2" spans="1:13">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="16.2" spans="1:14">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
     </row>
-    <row r="3" ht="16.2" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+    <row r="3" ht="16.2" spans="1:14">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
